--- a/data/trans_orig/P0901-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43257</t>
+          <t>43248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71925</t>
+          <t>71649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70218</t>
+          <t>71155</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104010</t>
+          <t>105536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122907</t>
+          <t>124085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168298</t>
+          <t>167001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>622087</t>
+          <t>622363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>650755</t>
+          <t>650764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>584341</t>
+          <t>582815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>618133</t>
+          <t>617196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1214065</t>
+          <t>1215362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1259456</t>
+          <t>1258278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77619</t>
+          <t>77493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116422</t>
+          <t>114858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>135981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182148</t>
+          <t>183848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219547</t>
+          <t>220557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>279371</t>
+          <t>282358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>845378</t>
+          <t>846942</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>884181</t>
+          <t>884307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>786245</t>
+          <t>784545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>833217</t>
+          <t>832412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1650822</t>
+          <t>1647835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1710646</t>
+          <t>1709636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44882</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74942</t>
+          <t>74914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101818</t>
+          <t>101186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139836</t>
+          <t>142351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154038</t>
+          <t>154112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204025</t>
+          <t>204754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603567</t>
+          <t>603595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633627</t>
+          <t>633130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>544005</t>
+          <t>541490</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582023</t>
+          <t>582655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1158325</t>
+          <t>1157596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1208312</t>
+          <t>1208238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69571</t>
+          <t>71366</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104675</t>
+          <t>105987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165954</t>
+          <t>163783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215956</t>
+          <t>214830</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244869</t>
+          <t>246602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305743</t>
+          <t>308948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>837547</t>
+          <t>836235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872651</t>
+          <t>870856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>822656</t>
+          <t>823782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>872658</t>
+          <t>874829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1675091</t>
+          <t>1671886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1735965</t>
+          <t>1734232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>264385</t>
+          <t>264894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>331126</t>
+          <t>336158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>507095</t>
+          <t>510656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>596362</t>
+          <t>594358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>795998</t>
+          <t>795588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>909314</t>
+          <t>900460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2945417</t>
+          <t>2940385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3012158</t>
+          <t>3011649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2782835</t>
+          <t>2784839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2872102</t>
+          <t>2868541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5746427</t>
+          <t>5755281</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5859743</t>
+          <t>5860153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73421</t>
+          <t>73477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109073</t>
+          <t>110183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,77 +2700,77 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>153343</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>128489</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>174328</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>244080</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>217049</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>273249</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>17,43%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>15,5%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>153343</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>132269</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>176301</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>244080</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>216501</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>274310</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>594396</t>
+          <t>593286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>630048</t>
+          <t>629992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,82 +2808,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>84,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>543707</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>522722</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>568561</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>78,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>81,57%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1156439</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1127270</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1183470</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>80,49%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>84,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>543707</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>520749</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>564781</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>74,71%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>81,02%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1095</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1156439</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1126209</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1184018</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>82,57%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>80,41%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109305</t>
+          <t>108130</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152842</t>
+          <t>152123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206376</t>
+          <t>205873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>258793</t>
+          <t>262494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>325168</t>
+          <t>328414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>396342</t>
+          <t>399549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>865105</t>
+          <t>865824</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>908642</t>
+          <t>909817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>773391</t>
+          <t>769690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>825808</t>
+          <t>826311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1653789</t>
+          <t>1650582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1724963</t>
+          <t>1721717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92184</t>
+          <t>94288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121960</t>
+          <t>122002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168348</t>
+          <t>167024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188427</t>
+          <t>191419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>245380</t>
+          <t>248391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665439</t>
+          <t>663335</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>700730</t>
+          <t>699708</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608826</t>
+          <t>610150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655214</t>
+          <t>655172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1289417</t>
+          <t>1286406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1346370</t>
+          <t>1343378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97036</t>
+          <t>98334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141882</t>
+          <t>141370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187948</t>
+          <t>189022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241563</t>
+          <t>240934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>299762</t>
+          <t>300559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366555</t>
+          <t>365555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>805857</t>
+          <t>806369</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>850703</t>
+          <t>849405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>810338</t>
+          <t>810967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>863953</t>
+          <t>862879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1633085</t>
+          <t>1634085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1699878</t>
+          <t>1699081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>377124</t>
+          <t>373017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>452238</t>
+          <t>456133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>692353</t>
+          <t>690758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>785922</t>
+          <t>793204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1091513</t>
+          <t>1089810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1219392</t>
+          <t>1217156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2974541</t>
+          <t>2970646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3049655</t>
+          <t>3053762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2772387</t>
+          <t>2765105</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2865956</t>
+          <t>2867551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5765696</t>
+          <t>5767932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5893575</t>
+          <t>5895278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,4%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>70780</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107797</t>
+          <t>107138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137344</t>
+          <t>137242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181477</t>
+          <t>183390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>220638</t>
+          <t>220108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>274532</t>
+          <t>277933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>567003</t>
+          <t>567662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602800</t>
+          <t>604020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>491362</t>
+          <t>489449</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>535495</t>
+          <t>535597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1073107</t>
+          <t>1069706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1127001</t>
+          <t>1127531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84221</t>
+          <t>84792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123361</t>
+          <t>121348</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159720</t>
+          <t>159562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213935</t>
+          <t>213948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>256808</t>
+          <t>256244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323427</t>
+          <t>324916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>899070</t>
+          <t>901083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>938210</t>
+          <t>937639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>828978</t>
+          <t>828965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>883193</t>
+          <t>883351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1741917</t>
+          <t>1740428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1808536</t>
+          <t>1809100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>49534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81306</t>
+          <t>80607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122281</t>
+          <t>124032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168529</t>
+          <t>168839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183257</t>
+          <t>181282</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>238524</t>
+          <t>241413</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>678945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>709808</t>
+          <t>710018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>616482</t>
+          <t>616172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>662730</t>
+          <t>660979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1306039</t>
+          <t>1303150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1361306</t>
+          <t>1363281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83366</t>
+          <t>83649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124763</t>
+          <t>123242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172854</t>
+          <t>173488</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227536</t>
+          <t>228333</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>270275</t>
+          <t>266461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>335385</t>
+          <t>335079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>854201</t>
+          <t>853918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>816243</t>
+          <t>815446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>870925</t>
+          <t>870291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1645961</t>
+          <t>1646267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1711071</t>
+          <t>1714885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>322135</t>
+          <t>323257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>392663</t>
+          <t>393536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>641640</t>
+          <t>639480</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>740543</t>
+          <t>736634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>981712</t>
+          <t>987151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1107494</t>
+          <t>1107887</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3001687</t>
+          <t>3000814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3072215</t>
+          <t>3071093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2803999</t>
+          <t>2807908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2902902</t>
+          <t>2905062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5831398</t>
+          <t>5831005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5957180</t>
+          <t>5951741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78800</t>
+          <t>79289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114638</t>
+          <t>114124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122192</t>
+          <t>123448</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152985</t>
+          <t>155201</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211009</t>
+          <t>210660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258789</t>
+          <t>260361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>520300</t>
+          <t>520814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>556138</t>
+          <t>555649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>522227</t>
+          <t>520011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>553020</t>
+          <t>551764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1051361</t>
+          <t>1049789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1099141</t>
+          <t>1099490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62611</t>
+          <t>51935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156370</t>
+          <t>154950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174274</t>
+          <t>176106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213276</t>
+          <t>216834</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201863</t>
+          <t>206070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>361848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1036494</t>
+          <t>1037914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1130253</t>
+          <t>1140929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>743764</t>
+          <t>740206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>782766</t>
+          <t>780934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1790241</t>
+          <t>1788056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1948041</t>
+          <t>1943834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89374</t>
+          <t>90256</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126968</t>
+          <t>127607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75934</t>
+          <t>66030</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186238</t>
+          <t>185456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162320</t>
+          <t>167528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288954</t>
+          <t>292270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577712</t>
+          <t>577073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>615306</t>
+          <t>614424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>747128</t>
+          <t>747910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>857432</t>
+          <t>867336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1349092</t>
+          <t>1345776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1475726</t>
+          <t>1470518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111823</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154296</t>
+          <t>152129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185238</t>
+          <t>187818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>255382</t>
+          <t>259044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>317532</t>
+          <t>315034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>396488</t>
+          <t>392635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>770874</t>
+          <t>773041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>813347</t>
+          <t>814274</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>839550</t>
+          <t>835888</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>909694</t>
+          <t>907114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1623614</t>
+          <t>1627467</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1702570</t>
+          <t>1705068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>356462</t>
+          <t>344105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>503192</t>
+          <t>500524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>559095</t>
+          <t>566674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>760672</t>
+          <t>762632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1003297</t>
+          <t>990136</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1231605</t>
+          <t>1238738</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2954461</t>
+          <t>2957129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3101191</t>
+          <t>3113548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2899878</t>
+          <t>2897918</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3101455</t>
+          <t>3093876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5886597</t>
+          <t>5879464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6114905</t>
+          <t>6128066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0901-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43248</t>
+          <t>43684</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71649</t>
+          <t>70389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71155</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105536</t>
+          <t>103609</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>124085</t>
+          <t>123136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167001</t>
+          <t>166387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>622363</t>
+          <t>623623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>650764</t>
+          <t>650328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582815</t>
+          <t>584742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>617196</t>
+          <t>619437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1215362</t>
+          <t>1215976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1258278</t>
+          <t>1259227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77493</t>
+          <t>77316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114858</t>
+          <t>114415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135981</t>
+          <t>132467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183848</t>
+          <t>181076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>220557</t>
+          <t>223251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>282358</t>
+          <t>282201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>846942</t>
+          <t>847385</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>884307</t>
+          <t>884484</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>784545</t>
+          <t>787317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>832412</t>
+          <t>835926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1647835</t>
+          <t>1647992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1709636</t>
+          <t>1706942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45379</t>
+          <t>44514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74914</t>
+          <t>74218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101186</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142351</t>
+          <t>142169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154112</t>
+          <t>154171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204754</t>
+          <t>203789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603595</t>
+          <t>604291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633130</t>
+          <t>633995</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>541490</t>
+          <t>541672</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582655</t>
+          <t>581266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1157596</t>
+          <t>1158561</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1208238</t>
+          <t>1208179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71366</t>
+          <t>71026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105987</t>
+          <t>103973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163783</t>
+          <t>163276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214830</t>
+          <t>213469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246602</t>
+          <t>248847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308948</t>
+          <t>311622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836235</t>
+          <t>838249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870856</t>
+          <t>871196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>823782</t>
+          <t>825143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>874829</t>
+          <t>875336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1671886</t>
+          <t>1669212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1734232</t>
+          <t>1731987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>264894</t>
+          <t>266224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>336158</t>
+          <t>332220</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>510656</t>
+          <t>509670</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>594358</t>
+          <t>596973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>795588</t>
+          <t>795572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>900460</t>
+          <t>901563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2940385</t>
+          <t>2944323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3011649</t>
+          <t>3010319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2784839</t>
+          <t>2782224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2868541</t>
+          <t>2869527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5755281</t>
+          <t>5754178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5860153</t>
+          <t>5860169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>71695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110183</t>
+          <t>109695</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128489</t>
+          <t>131890</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174328</t>
+          <t>175762</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>217049</t>
+          <t>215649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>273249</t>
+          <t>272367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>593286</t>
+          <t>593774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>629992</t>
+          <t>631774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>522722</t>
+          <t>521288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>568561</t>
+          <t>565160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1127270</t>
+          <t>1128152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1183470</t>
+          <t>1184870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108130</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152123</t>
+          <t>150650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205873</t>
+          <t>205313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262494</t>
+          <t>261394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>328414</t>
+          <t>325669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399549</t>
+          <t>394941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>865824</t>
+          <t>867297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>909817</t>
+          <t>912403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>769690</t>
+          <t>770790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>826311</t>
+          <t>826871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1650582</t>
+          <t>1655190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1721717</t>
+          <t>1724462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,11%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>58067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94288</t>
+          <t>93987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122002</t>
+          <t>122920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167024</t>
+          <t>166710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191419</t>
+          <t>190687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248391</t>
+          <t>245591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663335</t>
+          <t>663636</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>699708</t>
+          <t>699556</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>610150</t>
+          <t>610464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655172</t>
+          <t>654254</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286406</t>
+          <t>1289206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1343378</t>
+          <t>1344110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98334</t>
+          <t>98644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141370</t>
+          <t>141698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189022</t>
+          <t>187057</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240934</t>
+          <t>239916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>300559</t>
+          <t>297607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>365555</t>
+          <t>365554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>806369</t>
+          <t>806041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849405</t>
+          <t>849095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>810967</t>
+          <t>811985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>862879</t>
+          <t>864844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1634085</t>
+          <t>1634086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1699081</t>
+          <t>1702033</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>373017</t>
+          <t>372736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>456133</t>
+          <t>457774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>690758</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>793204</t>
+          <t>793882</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1089810</t>
+          <t>1091529</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1217156</t>
+          <t>1218293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2970646</t>
+          <t>2969005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3053762</t>
+          <t>3054043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2765105</t>
+          <t>2764427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2867551</t>
+          <t>2864106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5767932</t>
+          <t>5766795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5895278</t>
+          <t>5893559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70780</t>
+          <t>71153</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107138</t>
+          <t>106961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137242</t>
+          <t>134955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183390</t>
+          <t>181435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>220108</t>
+          <t>218265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277933</t>
+          <t>277744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>567662</t>
+          <t>567839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>604020</t>
+          <t>603647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>489449</t>
+          <t>491404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>535597</t>
+          <t>537884</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1069706</t>
+          <t>1069895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1127531</t>
+          <t>1129374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84792</t>
+          <t>83132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121348</t>
+          <t>126298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159562</t>
+          <t>160196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213948</t>
+          <t>211994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>256244</t>
+          <t>256582</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324916</t>
+          <t>322897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>901083</t>
+          <t>896133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>937639</t>
+          <t>939299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>828965</t>
+          <t>830919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>883351</t>
+          <t>882717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1740428</t>
+          <t>1742447</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1809100</t>
+          <t>1808762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49534</t>
+          <t>49302</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80607</t>
+          <t>81352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124032</t>
+          <t>125768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168839</t>
+          <t>169622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181282</t>
+          <t>180512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241413</t>
+          <t>237385</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>678945</t>
+          <t>678200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>710018</t>
+          <t>710250</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>616172</t>
+          <t>615389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660979</t>
+          <t>659243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303150</t>
+          <t>1307178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1363281</t>
+          <t>1364051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83649</t>
+          <t>84952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123242</t>
+          <t>122880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173488</t>
+          <t>171906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228333</t>
+          <t>224995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266461</t>
+          <t>267968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>335079</t>
+          <t>337012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>814325</t>
+          <t>814687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>853918</t>
+          <t>852615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>815446</t>
+          <t>818784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>870291</t>
+          <t>871873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1646267</t>
+          <t>1644334</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1714885</t>
+          <t>1713378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>323257</t>
+          <t>319716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>393536</t>
+          <t>394196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>639480</t>
+          <t>635291</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>736634</t>
+          <t>741820</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>987151</t>
+          <t>976514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1107887</t>
+          <t>1106741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3000814</t>
+          <t>3000154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3071093</t>
+          <t>3074634</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2807908</t>
+          <t>2802722</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2905062</t>
+          <t>2909251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5831005</t>
+          <t>5832151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5951741</t>
+          <t>5962378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95153</t>
+          <t>104156</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79289</t>
+          <t>85110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114124</t>
+          <t>123353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>138156</t>
+          <t>148844</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123448</t>
+          <t>134512</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155201</t>
+          <t>168652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>233309</t>
+          <t>252999</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>210660</t>
+          <t>227954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260361</t>
+          <t>281899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>539785</t>
+          <t>586061</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>520814</t>
+          <t>566864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>555649</t>
+          <t>605107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>537056</t>
+          <t>583690</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>520011</t>
+          <t>563882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>551764</t>
+          <t>598022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1076841</t>
+          <t>1169752</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1049789</t>
+          <t>1140852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1099490</t>
+          <t>1194797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>690217</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>690217</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634938</t>
+          <t>690217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675212</t>
+          <t>732534</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675212</t>
+          <t>732534</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675212</t>
+          <t>732534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310150</t>
+          <t>1422751</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310150</t>
+          <t>1422751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310150</t>
+          <t>1422751</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>115357</t>
+          <t>125433</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51935</t>
+          <t>105148</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154950</t>
+          <t>148330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>193821</t>
+          <t>218800</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176106</t>
+          <t>197824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216834</t>
+          <t>240476</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>309178</t>
+          <t>344233</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>206070</t>
+          <t>311548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>361848</t>
+          <t>374792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1077507</t>
+          <t>923484</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1037914</t>
+          <t>900587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1140929</t>
+          <t>943769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>763219</t>
+          <t>850928</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>740206</t>
+          <t>829252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>780934</t>
+          <t>871904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1840726</t>
+          <t>1774413</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1788056</t>
+          <t>1743854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1943834</t>
+          <t>1807098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957040</t>
+          <t>1069728</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957040</t>
+          <t>1069728</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957040</t>
+          <t>1069728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149904</t>
+          <t>2118646</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149904</t>
+          <t>2118646</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149904</t>
+          <t>2118646</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>106989</t>
+          <t>116146</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90256</t>
+          <t>96340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127607</t>
+          <t>138223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>137827</t>
+          <t>160417</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66030</t>
+          <t>142965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185456</t>
+          <t>181449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>244817</t>
+          <t>276563</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167528</t>
+          <t>249641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292270</t>
+          <t>306376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>597691</t>
+          <t>686927</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577073</t>
+          <t>664850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614424</t>
+          <t>706733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>795539</t>
+          <t>651842</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>747910</t>
+          <t>630810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>867336</t>
+          <t>669294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1393229</t>
+          <t>1338769</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1345776</t>
+          <t>1308956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1470518</t>
+          <t>1365691</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>131221</t>
+          <t>135268</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110896</t>
+          <t>116372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152129</t>
+          <t>158391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>228229</t>
+          <t>245972</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187818</t>
+          <t>223240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259044</t>
+          <t>270648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359450</t>
+          <t>381240</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>315034</t>
+          <t>349378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392635</t>
+          <t>412453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>793949</t>
+          <t>853104</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>773041</t>
+          <t>829981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814274</t>
+          <t>872000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>866703</t>
+          <t>873069</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>835888</t>
+          <t>848393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>907114</t>
+          <t>895801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1660652</t>
+          <t>1726173</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1627467</t>
+          <t>1694960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1705068</t>
+          <t>1758035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925170</t>
+          <t>988372</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925170</t>
+          <t>988372</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925170</t>
+          <t>988372</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2020102</t>
+          <t>2107413</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2020102</t>
+          <t>2107413</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2020102</t>
+          <t>2107413</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>448719</t>
+          <t>481003</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>438177</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>500524</t>
+          <t>522614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>698033</t>
+          <t>774032</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>566674</t>
+          <t>734684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>762632</t>
+          <t>817138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1146752</t>
+          <t>1255035</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>990136</t>
+          <t>1194796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1238738</t>
+          <t>1324056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3008934</t>
+          <t>3049576</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2957129</t>
+          <t>3007965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3113548</t>
+          <t>3092402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2962517</t>
+          <t>2959531</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2897918</t>
+          <t>2916425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3093876</t>
+          <t>2998879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5971450</t>
+          <t>6009107</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5879464</t>
+          <t>5940086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6128066</t>
+          <t>6069346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457653</t>
+          <t>3530579</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7118202</t>
+          <t>7264142</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
